--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104667_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104667_W24.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7457</v>
+        <v>5.6275</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1645</v>
+        <v>3.9112</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5812</v>
+        <v>1.7163</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6963</v>
+        <v>5.7075</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7622</v>
+        <v>-0.7421</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4585</v>
+        <v>6.4496</v>
       </c>
       <c r="J2" t="n">
-        <v>6.246</v>
+        <v>6.2252</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9871</v>
+        <v>0.9825</v>
       </c>
       <c r="L2" t="n">
-        <v>5.259</v>
+        <v>5.2427</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5497</v>
+        <v>-0.5177</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7493</v>
+        <v>-1.7246</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9506</v>
+        <v>-0.0801</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.747</v>
+        <v>0.0322</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2036</v>
+        <v>-0.1122</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.403</v>
+        <v>5.1922</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5369</v>
+        <v>5.2557</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1339</v>
+        <v>-0.0635</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3769</v>
+        <v>4.3479</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9222</v>
+        <v>1.9133</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4548</v>
+        <v>2.4346</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4412</v>
+        <v>5.3815</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8128</v>
+        <v>3.7814</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6284</v>
+        <v>1.6001</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0643</v>
+        <v>-1.0335</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8906</v>
+        <v>-1.8681</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9228</v>
+        <v>-0.1149</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6775</v>
+        <v>0.1019</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2453</v>
+        <v>-0.2168</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9369</v>
+        <v>4.328</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1307</v>
+        <v>3.5146</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8062</v>
+        <v>0.8134</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8368</v>
+        <v>3.8343</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2759</v>
+        <v>-0.2567</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1127</v>
+        <v>4.091</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3547</v>
+        <v>4.3231</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9697</v>
+        <v>0.9653</v>
       </c>
       <c r="L4" t="n">
-        <v>3.385</v>
+        <v>3.3579</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5179</v>
+        <v>-0.4888</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2457</v>
+        <v>-1.2219</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0341</v>
+        <v>-0.6445</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9557</v>
+        <v>-0.5323</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0784</v>
+        <v>-0.1122</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3705</v>
+        <v>2.2473</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1852</v>
+        <v>1.2827</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1854</v>
+        <v>0.9646</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6087</v>
+        <v>0.6011</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0359</v>
+        <v>-1.0449</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6446</v>
+        <v>1.6461</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1409</v>
+        <v>1.1179</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0906</v>
+        <v>-0.1109</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5321</v>
+        <v>-0.5168</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4027</v>
+        <v>0.2788</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0858</v>
+        <v>0.2135</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3169</v>
+        <v>0.0653</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4187</v>
+        <v>2.227</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7521</v>
+        <v>1.3056</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6666</v>
+        <v>0.9214</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7809</v>
+        <v>2.7848</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4012</v>
+        <v>-1.3934</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1822</v>
+        <v>4.1782</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1416</v>
+        <v>3.1157</v>
       </c>
       <c r="K6" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9826</v>
+        <v>2.9713</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3606</v>
+        <v>-0.3309</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3578</v>
+        <v>0.1754</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8257</v>
+        <v>0.427</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4679</v>
+        <v>-0.2516</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3497</v>
+        <v>1.5104</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2007</v>
+        <v>2.2917</v>
       </c>
       <c r="F7" t="n">
-        <v>1.149</v>
+        <v>-0.7813</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4769</v>
+        <v>0.989</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9958</v>
+        <v>-0.9653</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5189</v>
+        <v>1.9543</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7129</v>
+        <v>2.4521</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4515</v>
+        <v>0.0689</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1644</v>
+        <v>2.3832</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1897</v>
+        <v>-1.4631</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5443</v>
+        <v>-1.0342</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>-0.4289</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5071</v>
+        <v>-0.1615</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7561</v>
+        <v>-0.1604</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7509</v>
+        <v>-0.0011</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2248</v>
+        <v>1.3191</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1097</v>
+        <v>0.5452</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.885</v>
+        <v>0.7739</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9867</v>
+        <v>-0.4615</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9697</v>
+        <v>-2.982</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9565</v>
+        <v>2.5205</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4575</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0693</v>
+        <v>-1.4586</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3883</v>
+        <v>2.1597</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4708</v>
+        <v>-1.1626</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.039</v>
+        <v>-1.5233</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4318</v>
+        <v>0.3608</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4425</v>
+        <v>0.4634</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3478</v>
+        <v>0.1204</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.343</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6182</v>
+        <v>-0.7003</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0064</v>
+        <v>-2.3286</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3882</v>
+        <v>1.6283</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4789</v>
+        <v>-2.4917</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0417</v>
+        <v>-2.0475</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4372</v>
+        <v>-0.4442</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8372</v>
+        <v>-1.8603</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4586</v>
+        <v>-1.4726</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6417</v>
+        <v>-0.6314</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.131</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2994</v>
+        <v>0.0161</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1685</v>
+        <v>0.0501</v>
       </c>
       <c r="V9" t="n">
-        <v>2.4102</v>
+        <v>2.4082</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9364</v>
+        <v>-0.858</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2162</v>
+        <v>0.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1526</v>
+        <v>-1.258</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3995</v>
+        <v>-0.3922</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.117</v>
+        <v>-0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2825</v>
+        <v>-0.2799</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7695</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1721</v>
+        <v>-1.1617</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2589</v>
+        <v>-0.1974</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>-0.3695</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2976</v>
+        <v>0.1721</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5999</v>
+        <v>-0.9018</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4653</v>
+        <v>-0.9567</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1346</v>
+        <v>0.0549</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9065</v>
+        <v>-0.9132</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1947</v>
+        <v>-0.198</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2038</v>
+        <v>0.1772</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9555</v>
+        <v>0.9373</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7517</v>
+        <v>-0.7601</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1103</v>
+        <v>-1.0904</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5762</v>
+        <v>0.122</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6956</v>
+        <v>-0.1535</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1195</v>
+        <v>0.2755</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>19.2948</v>
+        <v>19.9914</v>
       </c>
       <c r="E12" t="n">
-        <v>14.8243</v>
+        <v>15.2214</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4705</v>
+        <v>4.77</v>
       </c>
       <c r="G12" t="n">
-        <v>14.0245</v>
+        <v>14.006</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.8719</v>
+        <v>-7.828900000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>21.8968</v>
+        <v>21.835</v>
       </c>
       <c r="J12" t="n">
-        <v>22.6341</v>
+        <v>22.403</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5761</v>
+        <v>4.458200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>18.0582</v>
+        <v>17.9448</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.609200000000001</v>
+        <v>-8.3969</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.4482</v>
+        <v>-12.2869</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8387</v>
+        <v>3.890100000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>5.6709</v>
+        <v>5.690900000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R12" t="n">
-        <v>19.2808</v>
+        <v>19.3485</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7865000000000001</v>
+        <v>-0.09259999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0131</v>
+        <v>-0.3046</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2265000000000001</v>
+        <v>0.2121000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3856000000000004</v>
+        <v>0.3870999999999996</v>
       </c>
       <c r="W12" t="n">
-        <v>6.8133</v>
+        <v>6.7811</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.427700000000001</v>
+        <v>-6.394</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5303</v>
+        <v>4.2538</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9249</v>
+        <v>4.8354</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3945</v>
+        <v>-0.5816</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9344</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8774</v>
+        <v>2.8669</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1619</v>
+        <v>3.1404</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1619</v>
+        <v>3.1404</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2275</v>
+        <v>-2.2034</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6621</v>
+        <v>1.3867</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8026</v>
+        <v>0.7453</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8595</v>
+        <v>0.6415</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,37 +1501,37 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0822</v>
+        <v>-0.0799</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1195</v>
+        <v>-0.1171</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1517</v>
+        <v>-0.1496</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0696</v>
+        <v>0.0697</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0696</v>
+        <v>0.0697</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9595</v>
+        <v>-0.8273</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3762</v>
+        <v>0.735</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3356</v>
+        <v>-1.5623</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.9721</v>
+        <v>0.731</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4374</v>
+        <v>1.4218</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.4096</v>
+        <v>-0.6909</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0735</v>
+        <v>3.0951</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2255</v>
+        <v>2.4993</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.152</v>
+        <v>0.5958</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0457</v>
+        <v>-2.3642</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.788</v>
+        <v>-1.0775</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2576</v>
+        <v>-1.2866</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9212</v>
+        <v>-0.3322</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8166</v>
+        <v>-0.0838</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1047</v>
+        <v>-0.2483</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2534</v>
+        <v>-0.3155</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2205</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5935</v>
+        <v>-0.9133</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6271</v>
+        <v>0.0519</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1522</v>
+        <v>0.4765</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3853</v>
+        <v>1.5397</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.5375</v>
+        <v>-1.0632</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2726</v>
+        <v>2.2915</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9843</v>
+        <v>1.3682</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7117</v>
+        <v>0.9233</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4248</v>
+        <v>-1.815</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.599</v>
+        <v>0.1715</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8258</v>
+        <v>-1.9865</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-3.8697</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2492</v>
+        <v>0.3937</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0393</v>
+        <v>-0.0375</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2099</v>
+        <v>0.4313</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7712</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7712</v>
+        <v>0.7025</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2753</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2832</v>
+        <v>0.5705</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5585</v>
+        <v>-1.4329</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7259</v>
+        <v>-1.9794</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4242</v>
+        <v>0.423</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6983</v>
+        <v>-2.4024</v>
       </c>
       <c r="J17" t="n">
-        <v>3.108</v>
+        <v>1.0425</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5109</v>
+        <v>1.1991</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5971</v>
+        <v>-0.1566</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3821</v>
+        <v>-3.0219</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0867</v>
+        <v>-0.7761</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2954</v>
+        <v>-2.2458</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7724</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5565</v>
+        <v>-0.581</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.216</v>
+        <v>-0.232</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3214</v>
+        <v>1.2472</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.277</v>
+        <v>-1.6241</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0718</v>
+        <v>-0.405</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3488</v>
+        <v>-1.2191</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2586</v>
+        <v>-1.2338</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1167</v>
+        <v>0.1286</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3753</v>
+        <v>-1.3624</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6434</v>
+        <v>0.6405</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.902</v>
+        <v>-1.8744</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3011</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0162</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2849</v>
+        <v>0.379</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0663</v>
+        <v>-1.7019</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5775</v>
+        <v>-0.9729</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4889</v>
+        <v>-0.729</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4726</v>
+        <v>-1.1532</v>
       </c>
       <c r="H19" t="n">
-        <v>1.544</v>
+        <v>1.3789</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0715</v>
+        <v>-2.5321</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3187</v>
+        <v>1.2531</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3884</v>
+        <v>1.9683</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9302</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8461</v>
+        <v>-2.4062</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1556</v>
+        <v>-0.5893</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0017</v>
+        <v>-1.8169</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8562</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8169</v>
+        <v>-0.2301</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.747</v>
+        <v>-0.3139</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0699</v>
+        <v>0.0838</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5463</v>
+        <v>-0.7739</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7071</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2474</v>
+        <v>-1.9448</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0872</v>
+        <v>-1.1929</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1602</v>
+        <v>-0.7519</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.287</v>
+        <v>-0.6614</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8903</v>
+        <v>0.9937</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3967</v>
+        <v>-1.6551</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3867</v>
+        <v>0.4541</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6375999999999999</v>
+        <v>0.8791</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-0.4249</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9003</v>
+        <v>-1.1155</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2526</v>
+        <v>0.1146</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.2301</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6125</v>
+        <v>-0.5111</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5263</v>
+        <v>-0.5089</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0862</v>
+        <v>-0.0022</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2534</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2485</v>
+        <v>-2.1994</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.293</v>
+        <v>-1.2176</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9555</v>
+        <v>-0.9817</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6599</v>
+        <v>-2.2888</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9927</v>
+        <v>-0.8931</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6526</v>
+        <v>-1.3957</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4673</v>
+        <v>-1.4009</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8832</v>
+        <v>-0.6485</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4159</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1272</v>
+        <v>-0.8879</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1096</v>
+        <v>-0.2446</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2368</v>
+        <v>-0.6433</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8154</v>
+        <v>0.6538</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6261</v>
+        <v>0.4109</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1893</v>
+        <v>0.2429</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0237</v>
+        <v>-3.0502</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6893</v>
+        <v>-0.7597</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3344</v>
+        <v>-2.2905</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0734</v>
+        <v>-3.0899</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2528</v>
+        <v>1.2359</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.3261</v>
+        <v>-4.3258</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8541</v>
+        <v>-0.9025</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0972</v>
+        <v>1.0645</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9513</v>
+        <v>-1.967</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2193</v>
+        <v>-2.1874</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.3749</v>
+        <v>-2.3588</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2253</v>
+        <v>0.2265</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0302</v>
+        <v>-0.0283</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2555</v>
+        <v>0.2548</v>
       </c>
       <c r="V22" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.4247</v>
+        <v>-9.607200000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9234</v>
+        <v>-5.4866</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5013</v>
+        <v>-4.1206</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.6027</v>
+        <v>-5.5945</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0793</v>
+        <v>-1.0799</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.5233</v>
+        <v>-4.5146</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2325</v>
+        <v>-1.2542</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2282</v>
+        <v>0.2133</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.3701</v>
+        <v>-4.3403</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.0626</v>
+        <v>-3.0471</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0074</v>
+        <v>-0.1917</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1727</v>
+        <v>0.171</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.2948</v>
+        <v>-18.5048</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.470499999999999</v>
+        <v>-4.7699</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.8243</v>
+        <v>-13.7348</v>
       </c>
       <c r="G24" t="n">
-        <v>-14.0247</v>
+        <v>-14.0061</v>
       </c>
       <c r="H24" t="n">
-        <v>7.8718</v>
+        <v>7.8287</v>
       </c>
       <c r="I24" t="n">
-        <v>-21.8967</v>
+        <v>-21.835</v>
       </c>
       <c r="J24" t="n">
-        <v>8.609399999999999</v>
+        <v>8.396799999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>12.4481</v>
+        <v>12.287</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.8388</v>
+        <v>-3.8902</v>
       </c>
       <c r="M24" t="n">
-        <v>-22.6342</v>
+        <v>-22.403</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.5759</v>
+        <v>-4.458</v>
       </c>
       <c r="O24" t="n">
-        <v>-18.0582</v>
+        <v>-17.9448</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.6707</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q24" t="n">
-        <v>-19.2809</v>
+        <v>-19.3487</v>
       </c>
       <c r="R24" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7865</v>
+        <v>1.5792</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2267</v>
+        <v>-0.2119999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.013</v>
+        <v>1.7915</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3855999999999997</v>
+        <v>-0.3869999999999998</v>
       </c>
       <c r="W24" t="n">
-        <v>6.4277</v>
+        <v>6.394</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.813199999999999</v>
+        <v>-6.7809</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104667_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104667_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.394</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104667_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-6.7809</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
